--- a/human_resources_forms/007_new_manager_welcome_quiz--human_resources_forms.xlsx
+++ b/human_resources_forms/007_new_manager_welcome_quiz--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>new_manager_welcome_quiz_page</t>
+          <t>new_manager_welcome_quiz_page_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New Manager Welcome Quiz</t>
+          <t>New Manager Welcome Quiz Page 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>new_manager_welcome_quiz_page</t>
+          <t>new_manager_welcome_quiz_page_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New Manager Welcome Quiz</t>
+          <t>New Manager Welcome Quiz Page 3</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>department_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>Department 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -878,7 +878,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>department_choices</t>
+          <t>department_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -895,7 +895,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>department_choices</t>
+          <t>department_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -912,7 +912,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>department_choices</t>
+          <t>department_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
